--- a/V5.0_双人执行工作区/00_共享/每日协调/DAILY_OBJECT_LOCK_20260831.xlsx
+++ b/V5.0_双人执行工作区/00_共享/每日协调/DAILY_OBJECT_LOCK_20260831.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对象锁" sheetId="1" r:id="Ra694faba5db04a88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对象锁" sheetId="1" r:id="R8028059f70ff429d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="10">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -58,8 +58,20 @@
       <x:color rgb="FFD0021B"/>
       <x:name val="Calibri"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF177A3F"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFC62828"/>
+      <x:name val="Calibri"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="9">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -99,6 +111,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFDEBEC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9F7E5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF1D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFDE3E3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -108,7 +135,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="21">
+  <x:cellXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -168,6 +195,27 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -548,7 +596,7 @@
       <x:c r="D2" s="1" t="str">
         <x:v>只读</x:v>
       </x:c>
-      <x:c r="E2" s="15" t="str">
+      <x:c r="E2" s="22" t="str">
         <x:v>冻结</x:v>
       </x:c>
       <x:c r="F2" s="1" t="str">
@@ -568,7 +616,7 @@
       <x:c r="D3" s="1" t="str">
         <x:v>不动</x:v>
       </x:c>
-      <x:c r="E3" s="15" t="str">
+      <x:c r="E3" s="22" t="str">
         <x:v>已交付</x:v>
       </x:c>
       <x:c r="F3" s="1" t="str">
@@ -586,33 +634,33 @@
         <x:v>A维护 / B只读复核</x:v>
       </x:c>
       <x:c r="D4" s="1" t="str">
-        <x:v>保留当前版本与已知缺口</x:v>
-      </x:c>
-      <x:c r="E4" s="15" t="str">
+        <x:v>保留当前版本；持续跟踪全表PK、资源锁和类型</x:v>
+      </x:c>
+      <x:c r="E4" s="22" t="str">
         <x:v>G2启动放行 / 非阻塞跟踪</x:v>
       </x:c>
       <x:c r="F4" s="1" t="str">
-        <x:v>21项行数证据在位；全表PK、资源锁和类型一致性继续跟踪</x:v>
+        <x:v>21项行数证据在位；本轮修复ODI精确金额与来源/布尔字段别名</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="44" customHeight="1">
       <x:c r="A5" s="1" t="str">
-        <x:v>共享模型</x:v>
+        <x:v>共享模型 / 正式Agent</x:v>
       </x:c>
       <x:c r="B5" s="1" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="C5" s="1" t="str">
-        <x:v>A维护 / B只读复核</x:v>
+        <x:v>A维护 / B独立复核</x:v>
       </x:c>
       <x:c r="D5" s="1" t="str">
-        <x:v>B不保存、不修改；DB06关系定向复测</x:v>
-      </x:c>
-      <x:c r="E5" s="17" t="str">
-        <x:v>G2启动放行 / DB06关系待核</x:v>
+        <x:v>发布R19、隐藏截断ODI原值、清缓存；提交六题复测</x:v>
+      </x:c>
+      <x:c r="E5" s="23" t="str">
+        <x:v>A修复已发布 / B_RETEST_REQUIRED</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
-        <x:v>V50_dim_date→V50_MVP_cycle_state月份筛选未传递；A核查关系方向/生效状态</x:v>
+        <x:v>AI-01/04/16/17 A侧实跑PASS；AI-19/20受后端20步上限阻塞</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="44" customHeight="1">
@@ -626,13 +674,13 @@
         <x:v>A维护 / B只读复核</x:v>
       </x:c>
       <x:c r="D6" s="1" t="str">
-        <x:v>保留A最新归档；B按证据只读复核</x:v>
-      </x:c>
-      <x:c r="E6" s="19" t="str">
-        <x:v>A页面完成 / B_REVIEW_PENDING / 恢复BLOCKED</x:v>
+        <x:v>页面不重复修改；保留两份页面XML分包</x:v>
+      </x:c>
+      <x:c r="E6" s="23" t="str">
+        <x:v>G3 PASS / 恢复BLOCKED</x:v>
       </x:c>
       <x:c r="F6" s="1" t="str">
-        <x:v>DB01/DB02/DB04待B本人签收；AI资源分包和干净目标恢复未完成；B不保存A对象</x:v>
+        <x:v>DB01/02/04已B签收；六页初验已闭环；AI资源分包与干净恢复未完成</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="44" customHeight="1">
@@ -643,16 +691,16 @@
         <x:v>B</x:v>
       </x:c>
       <x:c r="C7" s="1" t="str">
-        <x:v>B只读（AI协助文件核对）</x:v>
+        <x:v>B只读（A提供新增证据）</x:v>
       </x:c>
       <x:c r="D7" s="1" t="str">
-        <x:v>核对DB01/DB02/DB04、性能、XML状态与冲突</x:v>
-      </x:c>
-      <x:c r="E7" s="19" t="str">
-        <x:v>B_REVIEW_PENDING</x:v>
+        <x:v>页面项已闭环；继续复核AI与恢复材料</x:v>
+      </x:c>
+      <x:c r="E7" s="23" t="str">
+        <x:v>页面证据PASS / A07整体BLOCKED</x:v>
       </x:c>
       <x:c r="F7" s="1" t="str">
-        <x:v>B_REVIEW_A05_A07_20260831为草稿；B本人未签，不构成正式PASS</x:v>
+        <x:v>DB01/02/04/06及DB03/05均完成复核；G4/G5仍阻塞A07整体PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
@@ -666,13 +714,13 @@
         <x:v>B</x:v>
       </x:c>
       <x:c r="D8" s="1" t="str">
-        <x:v>保留完成页面，补正式证据与复测</x:v>
-      </x:c>
-      <x:c r="E8" s="17" t="str">
-        <x:v>PAGE_BUILD_DONE / FORMAL_BLOCKED</x:v>
+        <x:v>保留正式页面与证据包</x:v>
+      </x:c>
+      <x:c r="E8" s="22" t="str">
+        <x:v>PASS_B_SIGNED / A_REVIEW_PASS</x:v>
       </x:c>
       <x:c r="F8" s="1" t="str">
-        <x:v>默认与企业联动已取证；缺干净华为、财年/质量、性能、映射/对账和A复核</x:v>
+        <x:v>正式证据、性能、映射/对账和A只读复核均已闭环</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
@@ -686,13 +734,13 @@
         <x:v>B</x:v>
       </x:c>
       <x:c r="D9" s="1" t="str">
-        <x:v>保留实机联动预验收；补正式证据包</x:v>
-      </x:c>
-      <x:c r="E9" s="17" t="str">
-        <x:v>预验收PASS / 正式BLOCKED</x:v>
+        <x:v>保留正式页面与证据包</x:v>
+      </x:c>
+      <x:c r="E9" s="22" t="str">
+        <x:v>PASS_B_SIGNED / A_REVIEW_PASS</x:v>
       </x:c>
       <x:c r="F9" s="1" t="str">
-        <x:v>缺正式截图、10个source_id抽查、性能、三份验收文件和A复核</x:v>
+        <x:v>120/120来源抽查、性能、验收三件套和A只读复核已闭环</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="44" customHeight="1">
@@ -706,13 +754,13 @@
         <x:v>B</x:v>
       </x:c>
       <x:c r="D10" s="1" t="str">
-        <x:v>页面不重复搭建；等待A核查关系后定向复测</x:v>
-      </x:c>
-      <x:c r="E10" s="17" t="str">
-        <x:v>B页面预验收PASS / 联动BLOCKED</x:v>
+        <x:v>页面不重复搭建；保留三个月份关系复测证据</x:v>
+      </x:c>
+      <x:c r="E10" s="22" t="str">
+        <x:v>PASS_B_REVIEW</x:v>
       </x:c>
       <x:c r="F10" s="1" t="str">
-        <x:v>组件1月份筛选仍660条；A核查日期维→MVP周期表关系；B不改共享模型</x:v>
+        <x:v>日期维→MVP周期表关系修复已保存、清缓存并通过B独立复核</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="44" customHeight="1">
@@ -723,16 +771,16 @@
         <x:v>B</x:v>
       </x:c>
       <x:c r="C11" s="1" t="str">
-        <x:v>B</x:v>
+        <x:v>A修复 / B独立复核</x:v>
       </x:c>
       <x:c r="D11" s="1" t="str">
-        <x:v>按现有材料创建并冻结AI资源，先做5题冒烟</x:v>
-      </x:c>
-      <x:c r="E11" s="19" t="str">
-        <x:v>MATERIAL_READY / CONFIG_NOT_EXECUTED</x:v>
+        <x:v>B复测AI-01/04/16/17/19/20后执行25问全量</x:v>
+      </x:c>
+      <x:c r="E11" s="27" t="str">
+        <x:v>A_REPAIR_PARTIAL_PASS / G4_BLOCKED</x:v>
       </x:c>
       <x:c r="F11" s="1" t="str">
-        <x:v>正式AI实测0/25；报告视频和恢复材料未收口；不得按日期跳门槛</x:v>
+        <x:v>A侧AI-01/04/16/17 PASS；AI-19/20受20步上限阻塞；B不得以A自测代签</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="44" customHeight="1">
@@ -746,13 +794,13 @@
         <x:v>按职责共同</x:v>
       </x:c>
       <x:c r="D12" s="1" t="str">
-        <x:v>补20260831早报、门槛表、对象锁和复核草稿；晚报待当日实际结果</x:v>
-      </x:c>
-      <x:c r="E12" s="17" t="str">
-        <x:v>补充归档 / A+B待本人确认</x:v>
+        <x:v>更新门槛、对象锁、证据索引与A→B交接；保留真实阻塞</x:v>
+      </x:c>
+      <x:c r="E12" s="23" t="str">
+        <x:v>已更新 / A签已完成项</x:v>
       </x:c>
       <x:c r="F12" s="1" t="str">
-        <x:v>本记录不冒充09:00事前锁；AI不代替A/B签字；当前总状态仍BLOCKED</x:v>
+        <x:v>G3=PASS；G4/G5/G6=BLOCKED；A不代签B</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/V5.0_双人执行工作区/00_共享/每日协调/DAILY_OBJECT_LOCK_20260831.xlsx
+++ b/V5.0_双人执行工作区/00_共享/每日协调/DAILY_OBJECT_LOCK_20260831.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对象锁" sheetId="1" r:id="R8028059f70ff429d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对象锁" sheetId="1" r:id="R45b98b0a8dac4756"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -654,13 +654,13 @@
         <x:v>A维护 / B独立复核</x:v>
       </x:c>
       <x:c r="D5" s="1" t="str">
-        <x:v>发布R19、隐藏截断ODI原值、清缓存；提交六题复测</x:v>
+        <x:v>发布R20通用提示词、删除固定答案；完成六题真实问数</x:v>
       </x:c>
       <x:c r="E5" s="23" t="str">
-        <x:v>A修复已发布 / B_RETEST_REQUIRED</x:v>
+        <x:v>R20_3_PASS_3_FAIL / A_REPAIR_REQUIRED</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
-        <x:v>AI-01/04/16/17 A侧实跑PASS；AI-19/20受后端20步上限阻塞</x:v>
+        <x:v>AI-01/04/17 PASS；AI-16/19/20 FAIL；历史R12-R19不作最终通过依据</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="44" customHeight="1">
@@ -771,16 +771,16 @@
         <x:v>B</x:v>
       </x:c>
       <x:c r="C11" s="1" t="str">
-        <x:v>A修复 / B独立复核</x:v>
+        <x:v>A修复 / B暂不复核</x:v>
       </x:c>
       <x:c r="D11" s="1" t="str">
-        <x:v>B复测AI-01/04/16/17/19/20后执行25问全量</x:v>
+        <x:v>A修复AI-16/19/20并重跑全过后，B再执行六题独立复测与25问全量</x:v>
       </x:c>
       <x:c r="E11" s="27" t="str">
-        <x:v>A_REPAIR_PARTIAL_PASS / G4_BLOCKED</x:v>
+        <x:v>A_R20_3_PASS_3_FAIL / G4_BLOCKED</x:v>
       </x:c>
       <x:c r="F11" s="1" t="str">
-        <x:v>A侧AI-01/04/16/17 PASS；AI-19/20受20步上限阻塞；B不得以A自测代签</x:v>
+        <x:v>失败：元数据见manifest/4、MVP派生值错误、企业与储备治理统计错误；B不得代A修复</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="44" customHeight="1">
@@ -794,10 +794,10 @@
         <x:v>按职责共同</x:v>
       </x:c>
       <x:c r="D12" s="1" t="str">
-        <x:v>更新门槛、对象锁、证据索引与A→B交接；保留真实阻塞</x:v>
+        <x:v>更新门槛、对象锁、证据索引与R20交接；保留真实失败</x:v>
       </x:c>
       <x:c r="E12" s="23" t="str">
-        <x:v>已更新 / A签已完成项</x:v>
+        <x:v>已更新 / A仅签复测完成</x:v>
       </x:c>
       <x:c r="F12" s="1" t="str">
         <x:v>G3=PASS；G4/G5/G6=BLOCKED；A不代签B</x:v>
